--- a/examples/demos/10_time_series_and_construction.xlsx
+++ b/examples/demos/10_time_series_and_construction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC29958D-BCF7-4CB2-A14E-036BECE6446E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF372E7-1D50-4A4F-AF73-89BC92614CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Demo 10 — Time series, constructed copulas and named ranges</t>
   </si>
@@ -54,25 +54,40 @@
     <t>Tools demonstrated: create_time_series, wrap_with_output, run_simulation, set_named_range, create_copula, save_workbook_as</t>
   </si>
   <si>
-    <t>PREREQUISITES</t>
-  </si>
-  <si>
-    <t>Windows Excel with the ModelRisk add-in installed and licensed.</t>
-  </si>
-  <si>
-    <t>modelrisk-mcp connected to Claude (Claude Desktop / Claude Code).</t>
-  </si>
-  <si>
-    <t>PROMPT →  Open C:/Users/timou/source/repos/modelrisk-mcp/examples/demos/10_time_series_and_construction.xlsx in Excel</t>
+    <t>GETTING STARTED</t>
+  </si>
+  <si>
+    <t>You need: Windows Excel with the ModelRisk add-in installed and licensed, and modelrisk-mcp connected to Claude (Claude Desktop or Claude Code).</t>
+  </si>
+  <si>
+    <t>Save the demo gallery folder anywhere on your PC. Once per session, tell Claude where it is and which demo to open:</t>
+  </si>
+  <si>
+    <t>PROMPT →  My ModelRisk demo gallery is in &lt;your folder, e.g. Documents\modelrisk-demos&gt;. Open 10_time_series_and_construction.xlsx from there.</t>
+  </si>
+  <si>
+    <t>Claude remembers the folder for the rest of the session — later demos just need "Open &lt;file&gt; from the demo folder".</t>
+  </si>
+  <si>
+    <t>FAST TRACK — ONE PROMPT DOES IT ALL</t>
+  </si>
+  <si>
+    <t>In a hurry? This single prompt runs the whole demo end-to-end. Prefer to learn how it works? Skip to the numbered steps below — same result, one capability at a time.</t>
+  </si>
+  <si>
+    <t>PROMPT →  In this workbook: create a GBM time series for 2026-2030 in Model!B11:F11 with starting value 12400, mean growth 5% and volatility 12%; wrap Model!B14 as output "Rev2030"; run 5,000 iterations and give me the P10/P50/P90 of 2030 revenue; create a workbook-level named range "Rev2030" for Model!B14; and save a copy of the workbook as 10_time_series_DONE.xlsx in the same folder.</t>
+  </si>
+  <si>
+    <t>Expected: a stochastic revenue path, simulated fan of outcomes, a named range, and a saved copy.</t>
   </si>
   <si>
     <t>STEP-BY-STEP</t>
   </si>
   <si>
-    <t>Open the workbook (prerequisites prompt above) and look at the Model sheet: parameters in B5:B7, an empty path row B11:F11, and the key metric in B14.</t>
-  </si>
-  <si>
-    <t>PROMPT →  What is in the Model sheet of this workbook?</t>
+    <t>Open the workbook and look at the Model sheet: parameters in B5:B7, an empty path row B11:F11, and the key metric in B14.</t>
+  </si>
+  <si>
+    <t>PROMPT →  Open 10_time_series_and_construction.xlsx from the demo folder.</t>
   </si>
   <si>
     <t>Expected: Claude summarises the parameters and the empty stochastic-path row.</t>
@@ -217,7 +232,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +264,46 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
@@ -272,12 +327,42 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E4F92"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -322,43 +407,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -665,7 +758,7 @@
   <sheetPr>
     <tabColor rgb="FF0E4F92"/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -673,238 +766,265 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="22"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="20"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="18"/>
     </row>
     <row r="5" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="17"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
+      <c r="B9" s="18"/>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="16" t="s">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="17"/>
-    </row>
-    <row r="15" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="3">
+    </row>
+    <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="18"/>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="18"/>
+    </row>
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="13">
         <v>1</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="3">
+      <c r="B21" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="13">
         <v>2</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="3">
+      <c r="B25" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="13">
         <v>3</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="3">
+      <c r="B29" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="13">
         <v>4</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="3">
+      <c r="B33" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="13">
         <v>5</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="3">
+      <c r="B37" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="13">
         <v>6</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B39" s="17"/>
-    </row>
-    <row r="40" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B43" s="4" t="s">
+    <row r="43" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="12" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B45" s="17"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" s="5"/>
-      <c r="B46" s="1" t="s">
+      <c r="B45" s="18"/>
+    </row>
+    <row r="46" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A47" s="6"/>
-      <c r="B47" s="1" t="s">
+    <row r="47" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B47" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A48" s="7"/>
-      <c r="B48" s="1" t="s">
+    <row r="48" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B48" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A49" s="2"/>
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B49" s="10" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="51" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="18"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" s="14"/>
+      <c r="B52" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53" s="15"/>
+      <c r="B53" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A54" s="16"/>
+      <c r="B54" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55" s="11"/>
+      <c r="B55" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A14:B14"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A45:B45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -923,162 +1043,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="A1" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
+      <c r="A4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3">
         <v>12400</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="10">
+      <c r="A6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.05</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="10">
+      <c r="A7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="4">
         <v>0.12</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
+      <c r="A9" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>50</v>
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="14" spans="1:8" ht="42.75" x14ac:dyDescent="0.5">
-      <c r="A14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="14">
+      <c r="B12" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+    </row>
+    <row r="14" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="8">
         <f>F11</f>
         <v>0</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>54</v>
+      <c r="C14" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
+      <c r="A16" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
     </row>
     <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="15"/>
+      <c r="A17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="15"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1086,8 +1206,8 @@
     <mergeCell ref="B17:G18"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="B12:H12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/demos/10_time_series_and_construction.xlsx
+++ b/examples/demos/10_time_series_and_construction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF372E7-1D50-4A4F-AF73-89BC92614CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4C158C-0CD6-4CEC-B46F-EE0B25E9312F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,7 +75,7 @@
     <t>In a hurry? This single prompt runs the whole demo end-to-end. Prefer to learn how it works? Skip to the numbered steps below — same result, one capability at a time.</t>
   </si>
   <si>
-    <t>PROMPT →  In this workbook: create a GBM time series for 2026-2030 in Model!B11:F11 with starting value 12400, mean growth 5% and volatility 12%; wrap Model!B14 as output "Rev2030"; run 5,000 iterations and give me the P10/P50/P90 of 2030 revenue; create a workbook-level named range "Rev2030" for Model!B14; and save a copy of the workbook as 10_time_series_DONE.xlsx in the same folder.</t>
+    <t>PROMPT →  In this workbook: create a GBM time series for 2026-2030 in Model!B11:F11 with starting value 12400, mean growth 5% and volatility 12%; wrap Model!B14 as output "Rev2030"; run 5,000 iterations and give me the P10/P50/P90 of 2030 revenue; create a workbook-level named range "Revenue2030" for Model!B14; and save a copy of the workbook as 10_time_series_DONE.xlsx in the same folder.</t>
   </si>
   <si>
     <t>Expected: a stochastic revenue path, simulated fan of outcomes, a named range, and a saved copy.</t>
@@ -114,7 +114,7 @@
     <t>Name it for colleagues. A workbook-level named range makes the key cell addressable by name from anywhere.</t>
   </si>
   <si>
-    <t>PROMPT →  Create a workbook-level named range "Rev2030" pointing at Model!B14.</t>
+    <t>PROMPT →  Create a workbook-level named range "Revenue2030" pointing at Model!B14.</t>
   </si>
   <si>
     <t>Expected: The name Rev2030 appears in Excel's Name Box and resolves to Model!B14.</t>
@@ -407,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -438,13 +438,11 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -766,16 +764,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="17" t="s">
@@ -1003,7 +1001,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="16"/>
       <c r="B54" s="10" t="s">
         <v>42</v>
@@ -1043,40 +1041,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
@@ -1103,16 +1101,16 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="5"/>
@@ -1143,15 +1141,15 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="14" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
@@ -1166,38 +1164,38 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
       <c r="H18" s="9"/>
     </row>
   </sheetData>
@@ -1206,8 +1204,8 @@
     <mergeCell ref="B17:G18"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B12:H12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/demos/10_time_series_and_construction.xlsx
+++ b/examples/demos/10_time_series_and_construction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4C158C-0CD6-4CEC-B46F-EE0B25E9312F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8752C9F4-1779-4094-BAA4-B0D7DDEDF10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -437,20 +437,20 @@
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -764,19 +764,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="18"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="18"/>
@@ -797,7 +797,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="19" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="18"/>
@@ -823,7 +823,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="18"/>
@@ -844,7 +844,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="19" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="18"/>
@@ -958,7 +958,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="19" t="s">
         <v>34</v>
       </c>
       <c r="B45" s="18"/>
@@ -984,7 +984,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="19" t="s">
         <v>39</v>
       </c>
       <c r="B51" s="18"/>
@@ -1015,14 +1015,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A45:B45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1041,7 +1041,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="18"/>
@@ -1053,7 +1053,7 @@
       <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="18"/>
@@ -1065,7 +1065,7 @@
       <c r="H2" s="18"/>
     </row>
     <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="18"/>
@@ -1101,7 +1101,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="23" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="18"/>
@@ -1141,7 +1141,7 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>57</v>
       </c>
       <c r="C12" s="18"/>
@@ -1164,7 +1164,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="23" t="s">
         <v>60</v>
       </c>
       <c r="B16" s="18"/>
@@ -1179,7 +1179,7 @@
       <c r="A17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="22" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="18"/>
